--- a/系统版本号对应关系-20261018.xlsx
+++ b/系统版本号对应关系-20261018.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D10511A5-21C1-4196-8F63-51726417A92B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C41B545-9890-4FBB-A437-964A981E8867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8190" yWindow="3615" windowWidth="19065" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-45" yWindow="3240" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Windows10_22H2_amd64</t>
   </si>
@@ -57,19 +57,25 @@
     <t>Windows11_26H2B_amd64</t>
   </si>
   <si>
+    <t>Windows11_Canary_amd64</t>
+  </si>
+  <si>
+    <t>Windows11_25H2_amd64</t>
+  </si>
+  <si>
+    <t>最新大版本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Windows11_26H2_amd64</t>
-  </si>
-  <si>
-    <t>Windows11_Canary_amd64</t>
-  </si>
-  <si>
-    <t>Windows11_25H2B_amd64</t>
-  </si>
-  <si>
-    <t>Windows11_25H2_amd64</t>
-  </si>
-  <si>
-    <t>最新大版本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Windows11_26H2E_amd64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Windows11_26H2A_amd64</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -119,16 +125,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -411,243 +413,135 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="D2:H26"/>
+  <dimension ref="E3:F18"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="5" max="5" width="22.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="4:8">
-      <c r="D2" s="1"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="4:8">
-      <c r="D3" s="1"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-    </row>
-    <row r="4" spans="4:8">
-      <c r="D4" s="1"/>
-      <c r="E4" s="4" t="s">
+    <row r="3" spans="5:6">
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="5:6">
+      <c r="E4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="1">
         <v>19045</v>
       </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="4:8">
-      <c r="D5" s="1"/>
-      <c r="E5" s="4" t="s">
+    </row>
+    <row r="5" spans="5:6">
+      <c r="E5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="1">
         <v>19045</v>
       </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-    </row>
-    <row r="6" spans="4:8">
-      <c r="D6" s="1"/>
-      <c r="E6" s="4" t="s">
+    </row>
+    <row r="6" spans="5:6">
+      <c r="E6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="1">
         <v>19045</v>
       </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="4:8">
-      <c r="D7" s="1"/>
-      <c r="E7" s="4" t="s">
+    </row>
+    <row r="7" spans="5:6">
+      <c r="E7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="1">
         <v>17763</v>
       </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="4:8">
-      <c r="D8" s="1"/>
-      <c r="E8" s="4" t="s">
+    </row>
+    <row r="8" spans="5:6">
+      <c r="E8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="1">
         <v>17763</v>
       </c>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-    </row>
-    <row r="9" spans="4:8">
-      <c r="D9" s="1"/>
-      <c r="E9" s="4" t="s">
+    </row>
+    <row r="9" spans="5:6">
+      <c r="E9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="1">
         <v>22621</v>
       </c>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-    </row>
-    <row r="10" spans="4:8">
-      <c r="D10" s="1"/>
-      <c r="E10" s="4" t="s">
+    </row>
+    <row r="10" spans="5:6">
+      <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="1">
         <v>22631</v>
       </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-    </row>
-    <row r="11" spans="4:8">
-      <c r="D11" s="1"/>
-      <c r="E11" s="4" t="s">
+    </row>
+    <row r="11" spans="5:6">
+      <c r="E11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="1">
         <v>26100</v>
       </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-    </row>
-    <row r="12" spans="4:8">
-      <c r="D12" s="1"/>
-      <c r="E12" s="4" t="s">
+    </row>
+    <row r="12" spans="5:6">
+      <c r="E12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="1">
+        <v>26300</v>
+      </c>
+    </row>
+    <row r="13" spans="5:6">
+      <c r="E13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="1">
+        <v>26200</v>
+      </c>
+    </row>
+    <row r="14" spans="5:6">
+      <c r="E14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="1">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="15" spans="5:6">
+      <c r="E15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="1">
+        <v>28120</v>
+      </c>
+    </row>
+    <row r="16" spans="5:6">
+      <c r="E16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="1">
+        <v>28020</v>
+      </c>
+    </row>
+    <row r="17" spans="5:6">
+      <c r="E17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="1">
+        <v>26340</v>
+      </c>
+    </row>
+    <row r="18" spans="5:6">
+      <c r="E18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="2">
-        <v>26300</v>
-      </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-    </row>
-    <row r="13" spans="4:8">
-      <c r="D13" s="1"/>
-      <c r="E13" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="2">
-        <v>26200</v>
-      </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-    </row>
-    <row r="14" spans="4:8">
-      <c r="D14" s="1"/>
-      <c r="E14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="2">
-        <v>28000</v>
-      </c>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-    </row>
-    <row r="15" spans="4:8">
-      <c r="D15" s="1"/>
-      <c r="E15" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="2">
-        <v>28120</v>
-      </c>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-    </row>
-    <row r="16" spans="4:8">
-      <c r="D16" s="1"/>
-      <c r="E16" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="2">
-        <v>28020</v>
-      </c>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="4:8">
-      <c r="D17" s="1"/>
-      <c r="E17" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-    </row>
-    <row r="18" spans="4:8">
-      <c r="D18" s="1"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-    </row>
-    <row r="19" spans="4:8">
-      <c r="D19" s="1"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-    </row>
-    <row r="20" spans="4:8">
-      <c r="D20" s="1"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-    </row>
-    <row r="21" spans="4:8">
-      <c r="D21" s="1"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-    </row>
-    <row r="22" spans="4:8">
-      <c r="D22" s="1"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-    </row>
-    <row r="23" spans="4:8">
-      <c r="D23" s="1"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-    </row>
-    <row r="24" spans="4:8">
-      <c r="D24" s="1"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-    </row>
-    <row r="25" spans="4:8">
-      <c r="D25" s="1"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-    </row>
-    <row r="26" spans="4:8">
-      <c r="D26" s="1"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
